--- a/tools/_out/groupB_20261021/out/af/DesignTable_6900_SW2.xlsx
+++ b/tools/_out/groupB_20261021/out/af/DesignTable_6900_SW2.xlsx
@@ -1426,7 +1426,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="C6" t="n">
         <v>0.36373</v>
@@ -1465,7 +1465,7 @@
         <v>0.05</v>
       </c>
       <c r="O6" t="n">
-        <v>0.58</v>
+        <v>0.6</v>
       </c>
       <c r="P6" t="n">
         <v>0.1825</v>
@@ -1513,7 +1513,7 @@
         <v>0.1485</v>
       </c>
       <c r="AE6" t="n">
-        <v>0.19</v>
+        <v>0.21</v>
       </c>
       <c r="AF6" t="n">
         <v>0.481</v>
@@ -1531,7 +1531,7 @@
         <v>0.28494</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AL6" t="n">
         <v>0.22</v>
@@ -1589,12 +1589,12 @@
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>[BRENNAN-CELL 2026-10-21: W4@DRIVE, L2@DRIVE] Air-Way s105 only (double-pass 24 rows); NPSM male end fully published | MODEL: male ORB end: thread length + groove from the 6401/6405/6410 review tables (ORD-5700 groove, measured thread length; no tip chamfer modelled); W4 = ORB tip to the nut face (overall), L2 = ORB tip to the stem tip (Brennan 6900-08-08-O STEP: 1.550 / 1.270 = its record L / L1); body hex C2, nut hex C (Air-Way; Brennan C4 / C); female NPSM SWIVEL end, sectioned on the Brennan 1404 STEPs (one per NPSM size -02/-04/-06/-08/-12/-16/-20/-24/-32): nut hex = Air-Way C(2) (must equal the Brennan nut, checked per row) over the measured hex length, skirt cone and lip to the measured nut rear face; nut thread = straight NPSM of that size, minor = the Brennan value (-08: 0.759 = ASME B1.20.1 NPSM internal minor 0.7594 min), helical 60deg thread 0.8P deep over the measured length, 45deg countersink and 45deg relief to the measured counterbore; body stem with the measured 30deg male cone, OD and tip radius, neck behind the nut, body face at the measured distance behind the stem tip (Brennan); NUT FACE AT AIR-WAY W AND STEM TIP AT AIR-WAY L (user decision 2026-09-24: follow Air-Way - at -08 Air-Way W-L 0.33 vs Brennan 0.28, so the nut sits 0.05 further out than on the Brennan part); NUT AND BODY ARE ONE SOLID (Brennan STEPs are one solid too) - the nut/collar joint, the rear undercut under the nut lip, the slot at the collar, hex chamfers and fillets are NOT modelled; single manufacturer (Brennan); bore D1 (ORB side) / D (stem side) stepped at the body-hex mid-plane (ASSUMPTION, as 1404)</t>
+          <t>[BRENNAN-CELL 2026-10-21: L2@DRIVE] Air-Way s105 only (double-pass 24 rows); NPSM male end fully published | MODEL: male ORB end: thread length + groove from the 6401/6405/6410 review tables (ORD-5700 groove, measured thread length; no tip chamfer modelled); W4 = ORB tip to the nut face (overall), L2 = ORB tip to the stem tip (Brennan 6900-08-08-O STEP: 1.550 / 1.270 = its record L / L1); body hex C2, nut hex C (Air-Way; Brennan C4 / C); female NPSM SWIVEL end, sectioned on the Brennan 1404 STEPs (one per NPSM size -02/-04/-06/-08/-12/-16/-20/-24/-32): nut hex = Air-Way C(2) (must equal the Brennan nut, checked per row) over the measured hex length, skirt cone and lip to the measured nut rear face; nut thread = straight NPSM of that size, minor = the Brennan value (-08: 0.759 = ASME B1.20.1 NPSM internal minor 0.7594 min), helical 60deg thread 0.8P deep over the measured length, 45deg countersink and 45deg relief to the measured counterbore; body stem with the measured 30deg male cone, OD and tip radius, neck behind the nut, body face at the measured distance behind the stem tip (Brennan); NUT FACE AT AIR-WAY W AND STEM TIP AT AIR-WAY L (user decision 2026-09-24: follow Air-Way - at -08 Air-Way W-L 0.33 vs Brennan 0.28, so the nut sits 0.05 further out than on the Brennan part); NUT AND BODY ARE ONE SOLID (Brennan STEPs are one solid too) - the nut/collar joint, the rear undercut under the nut lip, the slot at the collar, hex chamfers and fillets are NOT modelled; single manufacturer (Brennan); bore D1 (ORB side) / D (stem side) stepped at the body-hex mid-plane (ASSUMPTION, as 1404)</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>A3 (user 2026-10-18): male ORB x female NPSM swivel straight - the old "female-JIC union internals" block was the wrong identity (removed 2026-10-21) | Brennan CAD record cross-check (2026-10-21; Air-Way values built): differ: W4 1.3 vs Brennan L 1.28; L2 1.19 vs Brennan L1 1.09 | Q-CONFLICT-6900-05-04-O: Air-Way W4 1.3 / L2 1.19 put the nut face 0.11 from the stem tip - the measured -04 NPSM swivel cannot be built (nut / stem order; Brennan 1404-04: 0.19) -&gt; both cells = the Brennan CAD record L 1.28 / L1 1.09 (user Q1 2026-10-20 "use brennans"; 2026-10-18 recommendation was "keep W4" - tell the user)</t>
+          <t>A3 (user 2026-10-18): male ORB x female NPSM swivel straight - the old "female-JIC union internals" block was the wrong identity (removed 2026-10-21) | Brennan CAD record cross-check (2026-10-21; Air-Way values built): differ: W4 1.3 vs Brennan L 1.28; L2 1.19 vs Brennan L1 1.09 | Q-CONFLICT-6900-05-04-O (user 2026-10-21 "do the recommended" = keep W4): Air-Way W4 1.3 kept; Air-Way L2 1.19 put the nut face 0.11 from the stem tip (the measured -04 NPSM swivel cannot be built) -&gt; L2 = the Brennan CAD record L1 1.09 (user Q1 2026-10-20 "use brennans"; Brennan prints L 1.28)</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
